--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -1938,9 +1938,10 @@
           <t>Q-W01</t>
         </is>
       </c>
-      <c r="B2">
-        <f>nein</f>
-        <v/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>=nein</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>-100</v>
@@ -1957,9 +1958,10 @@
           <t>Q-W05</t>
         </is>
       </c>
-      <c r="B3">
-        <f>Öl</f>
-        <v/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>=Öl</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>20</v>
@@ -1972,9 +1974,10 @@
           <t>Q-W05</t>
         </is>
       </c>
-      <c r="B4">
-        <f>Gas</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>=Gas</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
@@ -1987,9 +1990,10 @@
           <t>Q-W05</t>
         </is>
       </c>
-      <c r="B5">
-        <f>Nachtspeicher</f>
-        <v/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>=Nachtspeicher</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -2050,9 +2054,10 @@
           <t>Q-W10</t>
         </is>
       </c>
-      <c r="B9">
-        <f>sofort</f>
-        <v/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>=sofort</t>
+        </is>
       </c>
       <c r="C9" t="n">
         <v>25</v>
@@ -2065,9 +2070,10 @@
           <t>Q-W10</t>
         </is>
       </c>
-      <c r="B10">
-        <f>innerhalb 3 Monate</f>
-        <v/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>=innerhalb 3 Monate</t>
+        </is>
       </c>
       <c r="C10" t="n">
         <v>20</v>
@@ -2080,9 +2086,10 @@
           <t>Q-W10</t>
         </is>
       </c>
-      <c r="B11">
-        <f>innerhalb 6 Monate</f>
-        <v/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>=innerhalb 6 Monate</t>
+        </is>
       </c>
       <c r="C11" t="n">
         <v>10</v>
@@ -2095,9 +2102,10 @@
           <t>Q-W11</t>
         </is>
       </c>
-      <c r="B12">
-        <f>ja</f>
-        <v/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>=ja</t>
+        </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
@@ -2110,9 +2118,10 @@
           <t>Q-W12</t>
         </is>
       </c>
-      <c r="B13">
-        <f>ja</f>
-        <v/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>=ja</t>
+        </is>
       </c>
       <c r="C13" t="n">
         <v>10</v>
@@ -2125,9 +2134,10 @@
           <t>Q-W12</t>
         </is>
       </c>
-      <c r="B14">
-        <f>nein</f>
-        <v/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>=nein</t>
+        </is>
       </c>
       <c r="C14" t="n">
         <v>-10</v>
@@ -2156,9 +2166,10 @@
           <t>Q-P01</t>
         </is>
       </c>
-      <c r="B16">
-        <f>nein</f>
-        <v/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>=nein</t>
+        </is>
       </c>
       <c r="C16" t="n">
         <v>-100</v>
@@ -2175,9 +2186,10 @@
           <t>Q-P04</t>
         </is>
       </c>
-      <c r="B17">
-        <f>Süd</f>
-        <v/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>=Süd</t>
+        </is>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -2190,9 +2202,10 @@
           <t>Q-P04</t>
         </is>
       </c>
-      <c r="B18">
-        <f>Südost/Südwest</f>
-        <v/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>=Südost/Südwest</t>
+        </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
@@ -2221,9 +2234,10 @@
           <t>Q-P08</t>
         </is>
       </c>
-      <c r="B20">
-        <f>ja</f>
-        <v/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>=ja</t>
+        </is>
       </c>
       <c r="C20" t="n">
         <v>10</v>
@@ -2236,9 +2250,10 @@
           <t>Q-P09</t>
         </is>
       </c>
-      <c r="B21">
-        <f>vorhanden</f>
-        <v/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>=vorhanden</t>
+        </is>
       </c>
       <c r="C21" t="n">
         <v>10</v>
@@ -2251,9 +2266,10 @@
           <t>Q-P10</t>
         </is>
       </c>
-      <c r="B22">
-        <f>sofort</f>
-        <v/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>=sofort</t>
+        </is>
       </c>
       <c r="C22" t="n">
         <v>25</v>
@@ -2266,9 +2282,10 @@
           <t>Q-P10</t>
         </is>
       </c>
-      <c r="B23">
-        <f>innerhalb 3 Monate</f>
-        <v/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>=innerhalb 3 Monate</t>
+        </is>
       </c>
       <c r="C23" t="n">
         <v>20</v>
@@ -2281,9 +2298,10 @@
           <t>Q-P10</t>
         </is>
       </c>
-      <c r="B24">
-        <f>innerhalb 6 Monate</f>
-        <v/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>=innerhalb 6 Monate</t>
+        </is>
       </c>
       <c r="C24" t="n">
         <v>10</v>
@@ -2296,9 +2314,10 @@
           <t>Q-K05</t>
         </is>
       </c>
-      <c r="B25">
-        <f>sofort</f>
-        <v/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>=sofort</t>
+        </is>
       </c>
       <c r="C25" t="n">
         <v>25</v>
@@ -2311,9 +2330,10 @@
           <t>Q-K05</t>
         </is>
       </c>
-      <c r="B26">
-        <f>innerhalb 3 Monate</f>
-        <v/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>=innerhalb 3 Monate</t>
+        </is>
       </c>
       <c r="C26" t="n">
         <v>20</v>
@@ -2326,9 +2346,10 @@
           <t>Q-K05</t>
         </is>
       </c>
-      <c r="B27">
-        <f>innerhalb 6 Monate</f>
-        <v/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>=innerhalb 6 Monate</t>
+        </is>
       </c>
       <c r="C27" t="n">
         <v>10</v>
@@ -2341,9 +2362,10 @@
           <t>Q-B05</t>
         </is>
       </c>
-      <c r="B28">
-        <f>sofort</f>
-        <v/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>=sofort</t>
+        </is>
       </c>
       <c r="C28" t="n">
         <v>25</v>
@@ -2356,9 +2378,10 @@
           <t>Q-B05</t>
         </is>
       </c>
-      <c r="B29">
-        <f>innerhalb 3 Monate</f>
-        <v/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>=innerhalb 3 Monate</t>
+        </is>
       </c>
       <c r="C29" t="n">
         <v>20</v>
@@ -2371,9 +2394,10 @@
           <t>Q-B05</t>
         </is>
       </c>
-      <c r="B30">
-        <f>innerhalb 6 Monate</f>
-        <v/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>=innerhalb 6 Monate</t>
+        </is>
       </c>
       <c r="C30" t="n">
         <v>10</v>

--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -13,6 +13,8 @@
     <sheet name="Kaskade" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Gruende" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Wunschzeiten" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Objektarten" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Status" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +506,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>J</t>
@@ -513,7 +514,6 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>nein</t>
@@ -559,7 +559,6 @@
           <t>O01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,7 +581,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>N</t>
@@ -596,7 +594,6 @@
           <t>O02</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -619,7 +616,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>N</t>
@@ -633,7 +629,6 @@
           <t>O05</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -674,7 +669,6 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -697,7 +691,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>N</t>
@@ -711,7 +704,6 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -734,7 +726,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>J</t>
@@ -748,7 +739,6 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -771,7 +761,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>N</t>
@@ -780,8 +769,6 @@
       <c r="G9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -822,7 +809,6 @@
           <t>H02</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -858,8 +844,6 @@
       <c r="G11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -895,8 +879,6 @@
       <c r="G12" t="n">
         <v>11</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -919,7 +901,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>N</t>
@@ -928,8 +909,6 @@
       <c r="G13" t="n">
         <v>12</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -965,8 +944,6 @@
       <c r="G14" t="n">
         <v>13</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1002,8 +979,6 @@
       <c r="G15" t="n">
         <v>14</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1026,7 +1001,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>J</t>
@@ -1035,7 +1009,6 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>nein</t>
@@ -1081,7 +1054,6 @@
           <t>PO01</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1122,7 +1094,6 @@
           <t>PD01</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1158,8 +1129,6 @@
       <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1182,7 +1151,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>N</t>
@@ -1191,8 +1159,6 @@
       <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1228,8 +1194,6 @@
       <c r="G21" t="n">
         <v>6</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1252,7 +1216,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>J</t>
@@ -1266,7 +1229,6 @@
           <t>PO04</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1302,8 +1264,6 @@
       <c r="G23" t="n">
         <v>8</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1339,8 +1299,6 @@
       <c r="G24" t="n">
         <v>9</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1376,8 +1334,6 @@
       <c r="G25" t="n">
         <v>10</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1400,7 +1356,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>N</t>
@@ -1409,8 +1364,6 @@
       <c r="G26" t="n">
         <v>11</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1446,8 +1399,6 @@
       <c r="G27" t="n">
         <v>12</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1470,7 +1421,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>J</t>
@@ -1511,7 +1461,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>J</t>
@@ -1525,7 +1474,6 @@
           <t>KO05</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1548,7 +1496,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>N</t>
@@ -1557,8 +1504,6 @@
       <c r="G30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1594,8 +1539,6 @@
       <c r="G31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1631,8 +1574,6 @@
       <c r="G32" t="n">
         <v>5</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1668,8 +1609,6 @@
       <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1692,7 +1631,6 @@
           <t>janein</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>J</t>
@@ -1701,8 +1639,6 @@
       <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1738,8 +1674,6 @@
       <c r="G35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1762,7 +1696,6 @@
           <t>zahl</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>N</t>
@@ -1771,8 +1704,6 @@
       <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1808,8 +1739,6 @@
       <c r="G37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1845,8 +1774,6 @@
       <c r="G38" t="n">
         <v>5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1882,8 +1809,6 @@
       <c r="G39" t="n">
         <v>6</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1966,7 +1891,6 @@
       <c r="C3" t="n">
         <v>20</v>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1982,7 +1906,6 @@
       <c r="C4" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1998,7 +1921,6 @@
       <c r="C5" t="n">
         <v>15</v>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2014,7 +1936,6 @@
       <c r="C6" t="n">
         <v>15</v>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2030,7 +1951,6 @@
       <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2046,7 +1966,6 @@
       <c r="C8" t="n">
         <v>10</v>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2062,7 +1981,6 @@
       <c r="C9" t="n">
         <v>25</v>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2078,7 +1996,6 @@
       <c r="C10" t="n">
         <v>20</v>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2094,7 +2011,6 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2110,7 +2026,6 @@
       <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2126,7 +2041,6 @@
       <c r="C13" t="n">
         <v>10</v>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2142,7 +2056,6 @@
       <c r="C14" t="n">
         <v>-10</v>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2158,7 +2071,6 @@
       <c r="C15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2194,7 +2106,6 @@
       <c r="C17" t="n">
         <v>15</v>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2210,7 +2121,6 @@
       <c r="C18" t="n">
         <v>10</v>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2226,7 +2136,6 @@
       <c r="C19" t="n">
         <v>10</v>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2242,7 +2151,6 @@
       <c r="C20" t="n">
         <v>10</v>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2258,7 +2166,6 @@
       <c r="C21" t="n">
         <v>10</v>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2274,7 +2181,6 @@
       <c r="C22" t="n">
         <v>25</v>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2290,7 +2196,6 @@
       <c r="C23" t="n">
         <v>20</v>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2306,7 +2211,6 @@
       <c r="C24" t="n">
         <v>10</v>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2322,7 +2226,6 @@
       <c r="C25" t="n">
         <v>25</v>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2338,7 +2241,6 @@
       <c r="C26" t="n">
         <v>20</v>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2354,7 +2256,6 @@
       <c r="C27" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2370,7 +2271,6 @@
       <c r="C28" t="n">
         <v>25</v>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2386,7 +2286,6 @@
       <c r="C29" t="n">
         <v>20</v>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2402,7 +2301,6 @@
       <c r="C30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2482,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2594,6 +2492,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+14d</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mail_disqualifiziert</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>J</t>
         </is>
       </c>
@@ -2609,7 +2527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2975,6 +2893,108 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>zurueckgestellt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nachbearbeitung, noch nicht bereit für VOT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Zu teuer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kein Interesse mehr</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bleibt bei Öl/Gas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Woanders unterschrieben</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>J</t>
         </is>
@@ -3143,4 +3163,528 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bezeichnung</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>parteien_pflicht</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>erfassungs_wert</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EFH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Einfamilienhaus</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Einfamilienhaus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reihenhaus</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reihenhaus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Reihenendhaus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reihenhaus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MFH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mehrfamilienhaus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mehrfamilienhaus</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>farbe</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>gruppe</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>monday_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Neu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>#9aa4b2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Neuer Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>in_kontaktierung</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>In Kontaktierung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>#e87ba4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1. Kontaktversuch|2. Kontaktversuch|3. Kontaktversuch|4. Kontaktversuch|5. Kontaktversuch|erneuter Anruf|Telefongespräch|E-Mail|WhatsApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>qualifiziert</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Qualifiziert</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>#2a78d6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>zurueckgestellt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Zurückgestellt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>#c9a227</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pausiert</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Standby|Will sich selber zurückmelden|Nachbearbeitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nicht_erreicht</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nicht erreicht</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>#e05c8a</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>disqualifiziert</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Disqualifiziert - nicht erreicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>unqualifiziert</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unqualifiziert</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>#d64545</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>hauptboard</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>disqualifiziert</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Disqualifiziert</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Terminiert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>#7bc96f</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>angebotserstellung</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Terminiert|Teams Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>erfasst</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Erfasst</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>#5b6b8a</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>angebotserstellung</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Angebotserstellung|Vorab Angebot</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>angebot</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Angebot</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>#a0714f</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>angebotsversand</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Angebot versendet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gewonnen</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gewonnen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>#1baf7a</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>gewonnen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verloren</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>#6b7280</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>terminiert</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>verloren</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Einfamilienhaus</t>
+          <t>EFH</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reihenhaus</t>
+          <t>RMH</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reihenhaus</t>
+          <t>REH</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mehrfamilienhaus</t>
+          <t>MFH</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,6 @@
           <t>neu</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3654,7 +3653,6 @@
           <t>gewonnen</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3682,7 +3680,6 @@
           <t>verloren</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Qualifizierung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Klassen" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Kaskade" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruende" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Wunschzeiten" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Objektarten" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Status" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Lesehilfe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Qualifizierung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scoring" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Klassen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kaskade" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruende" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wunschzeiten" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Objektarten" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Status" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,6 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="160" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lead-Steuerdatei – Lesehilfe (v25, 05.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kaskade: Spalte wiedervorlage_nach wird seit v25 NICHT mehr ausgewertet – „Nicht erreicht“/„Mailbox“ setzen keine automatische Wiedervorlage; die Spalte aktion (mail_nicht_erreicht, mail_disqualifiziert) bleibt an die Versuchsnummer gekoppelt, letzter = Übergang nach Nicht erreicht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Status: Spalte label ist das Anzeige-Label der Phase (in_kontaktierung und qualifiziert tragen seit v25 beide „Kontaktiert“ – zwei Phasen dürfen dasselbe Label haben), board/gruppe = Zuordnung, board_label = Anzeigename des Boards (Hauptboard / Deals).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qualifizierung, Scoring, Klassen: seit v25 nicht aktiv (Parameter score_aktiv = aus); die Blätter bleiben unverändert liegen und werden nur eingelesen, nicht angewendet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gruende, Wunschzeiten, Objektarten: unverändert (siehe CLAUDE.md v12/v23).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1815,7 +1868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2307,7 +2360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2374,7 +2427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2521,7 +2574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3005,7 +3058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3165,7 +3218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3295,13 +3348,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3310,6 +3363,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3343,6 +3397,11 @@
           <t>monday_status</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>board_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3375,6 +3434,11 @@
           <t>Neuer Lead</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3384,7 +3448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>In Kontaktierung</t>
+          <t>Kontaktiert</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3405,6 +3469,11 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>1. Kontaktversuch|2. Kontaktversuch|3. Kontaktversuch|4. Kontaktversuch|5. Kontaktversuch|erneuter Anruf|Telefongespräch|E-Mail|WhatsApp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3485,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qualifiziert</t>
+          <t>Kontaktiert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#2a78d6</t>
+          <t>#e87ba4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3432,6 +3501,11 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>neu</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
         </is>
       </c>
     </row>
@@ -3466,6 +3540,11 @@
           <t>Standby|Will sich selber zurückmelden|Nachbearbeitung</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3498,6 +3577,11 @@
           <t>Disqualifiziert - nicht erreicht</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3530,6 +3614,11 @@
           <t>Disqualifiziert</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hauptboard</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3562,6 +3651,11 @@
           <t>Terminiert|Teams Meeting</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3594,6 +3688,11 @@
           <t>Angebotserstellung|Vorab Angebot</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3626,6 +3725,11 @@
           <t>Angebot versendet</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3653,6 +3757,11 @@
           <t>gewonnen</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Deals</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3678,6 +3787,11 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>verloren</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Deals</t>
         </is>
       </c>
     </row>

--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Wunschzeiten" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Objektarten" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Status" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Terminhinweise" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -463,6 +464,131 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>Gruende, Wunschzeiten, Objektarten: unverändert (siehe CLAUDE.md v12/v23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v29 (08.10.2026): Nurture entfällt – Blatt Kaskade Spalte nach_letztem (Standard mail_disqualifiziert) nennt die Aktion nach dem letzten Versuch; die Aktion mail_nurture wird nicht mehr ausgeführt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v29: Blatt Terminhinweise (sparte WP/PV/KL/WB/GW, reihenfolge, punkt) füllt den Baustein {sparten_hinweise} der Terminbestätigung – je Interesse eine Punkteliste; „(Punkte folgen)“ ist der Platzhalter, bis Claudia die Punkte nachreicht [OFFEN 1].</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sparte</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>reihenfolge</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>punkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WP</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
         </is>
       </c>
     </row>
@@ -2433,14 +2559,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -2468,6 +2594,11 @@
           <t>letzter</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>nach_letztem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2566,6 +2697,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>J</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mail_disqualifiziert</t>
         </is>
       </c>
     </row>

--- a/leadmanagement_logik_v1.xlsx
+++ b/leadmanagement_logik_v1.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,51 @@
         <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(Punkte folgen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DMS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>(Punkte folgen)</t>
         </is>
@@ -2631,7 +2676,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mail_nicht_erreicht</t>
+          <t>keine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2671,7 +2716,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mail_nicht_erreicht</t>
+          <t>keine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3200,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3240,6 +3285,11 @@
           <t>wochentage</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3267,6 +3317,11 @@
           <t>mo-fr</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3294,6 +3349,11 @@
           <t>mo-fr</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3321,6 +3381,11 @@
           <t>mo-fr</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3346,6 +3411,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>sa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nein</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3797,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unqualifiziert</t>
+          <t>Disqualifiziert</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
